--- a/kahoot/orientation/history/9_finnish_history__0002.xlsx
+++ b/kahoot/orientation/history/9_finnish_history__0002.xlsx
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Att en stat erövrar områden på andra kontinenter och utnyttjar deras resurser</t>
+          <t>Att en stat erövrar områden och utnyttjar deras resurser</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
